--- a/artifact-tables.xlsx
+++ b/artifact-tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anna/lamp/tyql/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DB3D4F-EE9B-934B-AF66-760B906A79DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9BD791-725F-DC43-ABDE-9312F46DE29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{C97E319E-3C7C-F248-853E-8BD1A6A75246}"/>
+    <workbookView xWindow="-20960" yWindow="-28300" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{C97E319E-3C7C-F248-853E-8BD1A6A75246}"/>
   </bookViews>
   <sheets>
     <sheet name="EXACT TABLE" sheetId="12" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="table-5" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="test_formulas" localSheetId="1">'compare-with-submitted'!$A$1:$O$59</definedName>
+    <definedName name="test_formulas" localSheetId="1">'compare-with-submitted'!$A$1:$U$59</definedName>
     <definedName name="test_formulas" localSheetId="6">'helper-calculations'!$A$1:$AC$110</definedName>
     <definedName name="test_formulas" localSheetId="4">large!$A$1:$Z$79</definedName>
     <definedName name="test_formulas" localSheetId="3">medium!$A$1:$Z$79</definedName>
@@ -287,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="139">
   <si>
     <t>Size</t>
   </si>
@@ -699,12 +699,18 @@
   <si>
     <t>&gt;&gt; INPUT SMALL CLEANED CSV HERE</t>
   </si>
+  <si>
+    <t>Exceeds error margin?</t>
+  </si>
+  <si>
+    <t>VS TYQL S: Docker artifact run by authors</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -781,6 +787,18 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -814,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -831,11 +849,523 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3370,31 +3900,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5EBAAEE-A4E0-E449-B206-A3FD57846453}">
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:AD57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
-    <col min="5" max="5" width="3.5" customWidth="1"/>
-    <col min="6" max="6" width="3.1640625" customWidth="1"/>
-    <col min="7" max="7" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
-    <col min="10" max="10" width="4.83203125" customWidth="1"/>
-    <col min="11" max="11" width="4.1640625" customWidth="1"/>
-    <col min="13" max="14" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" customWidth="1"/>
-    <col min="16" max="16" width="4.1640625" customWidth="1"/>
-    <col min="17" max="17" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="34.1640625" customWidth="1"/>
-    <col min="22" max="22" width="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" customWidth="1"/>
+    <col min="9" max="9" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.33203125" customWidth="1"/>
+    <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" customWidth="1"/>
+    <col min="18" max="18" width="24.33203125" customWidth="1"/>
+    <col min="19" max="19" width="12.1640625" customWidth="1"/>
+    <col min="20" max="20" width="20.6640625" customWidth="1"/>
+    <col min="21" max="21" width="17.5" customWidth="1"/>
+    <col min="22" max="22" width="4.1640625" customWidth="1"/>
+    <col min="23" max="23" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="25" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="34.1640625" customWidth="1"/>
+    <col min="28" max="28" width="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="65" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:30" ht="65" x14ac:dyDescent="0.75">
       <c r="B1" s="3" t="s">
         <v>125</v>
       </c>
@@ -3402,1081 +3940,1591 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="3"/>
+      <c r="W1" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="10" t="s">
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="L2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="Q2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="S2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="U2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="W2" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="7" t="s">
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="AC2" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3">
         <v>2.6917155098543302</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>23.906748928877501</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>0.97950985432733495</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>1.9824899884148401</v>
       </c>
-      <c r="H3">
+      <c r="J3" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>15.690817620389881</v>
       </c>
-      <c r="I3">
+      <c r="L3" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3">
         <v>1.0645302536876384</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="str">
         <f>medium!Q3</f>
         <v>DNF</v>
       </c>
-      <c r="M3" t="str">
+      <c r="Q3" t="b">
+        <f>medium!T26</f>
+        <v>1</v>
+      </c>
+      <c r="R3" t="str">
         <f>medium!R3</f>
         <v>DNF</v>
       </c>
-      <c r="N3" t="str">
+      <c r="S3" t="b">
+        <f>medium!U26</f>
+        <v>1</v>
+      </c>
+      <c r="T3" t="str">
         <f>medium!S3</f>
         <v>DNF</v>
       </c>
-      <c r="Q3" s="4" t="e">
-        <f>IF(AND(L3="DNF", B3="DNF"), "Both DNF",B3/ L3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R3" s="4" t="e">
-        <f t="shared" ref="R3:S3" si="0">IF(AND(M3="DNF", C3="DNF"), "Both DNF",C3/ M3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S3" s="4" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="8" t="e">
-        <f>IF(AND(L3="DNF", G3="DNF"), "Both DNF",G3/ L3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W3" s="8" t="e">
-        <f t="shared" ref="W3:X3" si="1">IF(AND(M3="DNF", H3="DNF"), "Both DNF",H3/ M3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X3" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U3" t="b">
+        <f>medium!V26</f>
+        <v>1</v>
+      </c>
+      <c r="W3" s="4" t="e">
+        <f>IF(AND(P3="DNF", B3="DNF"), "Both DNF", IF(AND(Q3=FALSE, C3=FALSE), "Both ~1x", B3/ P3))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X3" s="4" t="e">
+        <f>IF(AND(R3="DNF", D3="DNF"), "Both DNF", IF(AND(S3=FALSE, E3=FALSE), "Both ~1x",D3/ R3))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y3" s="4" t="e">
+        <f>IF(AND(T3="DNF", F3="DNF"), "Both DNF",IF(AND(G3=FALSE, U3=FALSE), "Both ~1x",F3/ T3))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="8" t="e">
+        <f>IF(AND(P3="DNF", I3="DNF"), "Both DNF",IF(AND(Q3=FALSE, J3=FALSE), "Both ~1x",I3/ P3))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC3" s="8" t="e">
+        <f>IF(AND(R3="DNF", K3="DNF"), "Both DNF", IF(AND(S3=FALSE, L3=FALSE), "Both ~1x",K3/ R3))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD3" s="8" t="e">
+        <f>IF(AND(T3="DNF", M3="DNF"), "Both DNF",IF(AND(U3=FALSE, N3=FALSE), "Both ~1x",M3/ T3))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4">
         <v>5.1147134744450202</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <v>178.45725348477001</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>0.89757356737222505</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>4.7717077270578354</v>
       </c>
-      <c r="H4">
+      <c r="J4" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>183.61995062247203</v>
       </c>
-      <c r="I4">
+      <c r="L4" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>0.96112832904344181</v>
       </c>
-      <c r="L4" t="str">
+      <c r="N4" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="str">
         <f>medium!Q4</f>
         <v>DNF</v>
       </c>
-      <c r="M4" t="str">
+      <c r="Q4" t="b">
+        <f>medium!T27</f>
+        <v>1</v>
+      </c>
+      <c r="R4" t="str">
         <f>medium!R4</f>
         <v>DNF</v>
       </c>
-      <c r="N4" t="str">
+      <c r="S4" t="b">
+        <f>medium!U27</f>
+        <v>1</v>
+      </c>
+      <c r="T4" t="str">
         <f>medium!S4</f>
         <v>DNF</v>
       </c>
-      <c r="Q4" s="4" t="e">
-        <f t="shared" ref="Q4:Q18" si="2">IF(AND(L4="DNF", B4="DNF"), "Both DNF",B4/ L4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R4" s="4" t="e">
-        <f t="shared" ref="R4:R18" si="3">IF(AND(M4="DNF", C4="DNF"), "Both DNF",C4/ M4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S4" s="4" t="e">
-        <f t="shared" ref="S4:S18" si="4">IF(AND(N4="DNF", D4="DNF"), "Both DNF",D4/ N4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="8" t="e">
-        <f t="shared" ref="V4:V18" si="5">IF(AND(L4="DNF", G4="DNF"), "Both DNF",G4/ L4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W4" s="8" t="e">
-        <f t="shared" ref="W4:W18" si="6">IF(AND(M4="DNF", H4="DNF"), "Both DNF",H4/ M4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X4" s="8" t="e">
-        <f t="shared" ref="X4:X18" si="7">IF(AND(N4="DNF", I4="DNF"), "Both DNF",I4/ N4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U4" t="b">
+        <f>medium!V27</f>
+        <v>1</v>
+      </c>
+      <c r="W4" s="4" t="e">
+        <f t="shared" ref="W4:W57" si="0">IF(AND(P4="DNF", B4="DNF"), "Both DNF", IF(AND(Q4=FALSE, C4=FALSE), "Both ~1x", B4/ P4))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X4" s="4" t="e">
+        <f t="shared" ref="X4:X57" si="1">IF(AND(R4="DNF", D4="DNF"), "Both DNF", IF(AND(S4=FALSE, E4=FALSE), "Both ~1x",D4/ R4))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y4" s="4" t="e">
+        <f t="shared" ref="Y4:Y57" si="2">IF(AND(T4="DNF", F4="DNF"), "Both DNF",IF(AND(G4=FALSE, U4=FALSE), "Both ~1x",F4/ T4))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="8" t="e">
+        <f t="shared" ref="AB4:AB57" si="3">IF(AND(P4="DNF", I4="DNF"), "Both DNF",IF(AND(Q4=FALSE, J4=FALSE), "Both ~1x",I4/ P4))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC4" s="8" t="e">
+        <f t="shared" ref="AC4:AC57" si="4">IF(AND(R4="DNF", K4="DNF"), "Both DNF", IF(AND(S4=FALSE, L4=FALSE), "Both ~1x",K4/ R4))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD4" s="8" t="e">
+        <f t="shared" ref="AD4:AD57" si="5">IF(AND(T4="DNF", M4="DNF"), "Both DNF",IF(AND(U4=FALSE, N4=FALSE), "Both ~1x",M4/ T4))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B5">
         <v>3.4410959361538702</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>331.37775069289103</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>0.92481717701272204</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>3.8045534943029908</v>
       </c>
-      <c r="H5">
+      <c r="J5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>408.16506931018881</v>
       </c>
-      <c r="I5">
+      <c r="L5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>0.92731685245362194</v>
       </c>
-      <c r="L5" t="str">
+      <c r="N5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="str">
         <f>medium!Q5</f>
         <v>DNF</v>
       </c>
-      <c r="M5" t="str">
+      <c r="Q5" t="b">
+        <f>medium!T28</f>
+        <v>1</v>
+      </c>
+      <c r="R5" t="str">
         <f>medium!R5</f>
         <v>DNF</v>
       </c>
-      <c r="N5" t="str">
+      <c r="S5" t="b">
+        <f>medium!U28</f>
+        <v>1</v>
+      </c>
+      <c r="T5" t="str">
         <f>medium!S5</f>
         <v>DNF</v>
       </c>
-      <c r="Q5" s="4" t="e">
+      <c r="U5" t="b">
+        <f>medium!V28</f>
+        <v>1</v>
+      </c>
+      <c r="W5" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X5" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y5" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R5" s="4" t="e">
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="8" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S5" s="4" t="e">
+      <c r="AC5" s="8" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="8" t="e">
+      <c r="AD5" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W5" s="8" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X5" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B6">
         <v>6.7273081114743896</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>1725.1112149047699</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>0.90190201878665199</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>6.396599893675984</v>
       </c>
-      <c r="H6">
+      <c r="J6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6">
         <v>1541.1704351366941</v>
       </c>
-      <c r="I6">
+      <c r="L6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1.0152020721872208</v>
       </c>
-      <c r="L6" t="str">
+      <c r="N6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="str">
         <f>medium!Q6</f>
         <v>DNF</v>
       </c>
-      <c r="M6" t="str">
+      <c r="Q6" t="b">
+        <f>medium!T29</f>
+        <v>1</v>
+      </c>
+      <c r="R6" t="str">
         <f>medium!R6</f>
         <v>DNF</v>
       </c>
-      <c r="N6" t="str">
+      <c r="S6" t="b">
+        <f>medium!U29</f>
+        <v>1</v>
+      </c>
+      <c r="T6" t="str">
         <f>medium!S6</f>
         <v>DNF</v>
       </c>
-      <c r="Q6" s="4" t="e">
+      <c r="U6" t="b">
+        <f>medium!V29</f>
+        <v>1</v>
+      </c>
+      <c r="W6" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X6" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y6" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R6" s="4" t="e">
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="8" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S6" s="4" t="e">
+      <c r="AC6" s="8" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="8" t="e">
+      <c r="AD6" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W6" s="8" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X6" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B7">
         <v>3.2105488117626901</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>122</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>0.74722174730723201</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>2.9770415699514667</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>122</v>
       </c>
-      <c r="I7">
+      <c r="L7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>0.76117324330027425</v>
       </c>
-      <c r="L7" t="str">
+      <c r="N7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="str">
         <f>medium!Q7</f>
         <v>DNF</v>
       </c>
-      <c r="M7" t="str">
+      <c r="Q7" t="b">
+        <f>medium!T30</f>
+        <v>1</v>
+      </c>
+      <c r="R7" t="str">
         <f>medium!R7</f>
         <v>DNF</v>
       </c>
-      <c r="N7" t="str">
+      <c r="S7" t="b">
+        <f>medium!U30</f>
+        <v>1</v>
+      </c>
+      <c r="T7" t="str">
         <f>medium!S7</f>
         <v>DNF</v>
       </c>
-      <c r="Q7" s="4" t="e">
+      <c r="U7" t="b">
+        <f>medium!V30</f>
+        <v>1</v>
+      </c>
+      <c r="W7" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y7" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R7" s="4" t="str">
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC7" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="AD7" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>2.51048566916386</v>
+      </c>
+      <c r="C8" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>51.666345031458803</v>
+      </c>
+      <c r="E8" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1.0305372753522599</v>
+      </c>
+      <c r="G8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>2.5325725846173173</v>
+      </c>
+      <c r="J8" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>48.818683080503398</v>
+      </c>
+      <c r="L8" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0.9636110000033058</v>
+      </c>
+      <c r="N8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="str">
+        <f>medium!Q8</f>
+        <v>DNF</v>
+      </c>
+      <c r="Q8" t="b">
+        <f>medium!T31</f>
+        <v>1</v>
+      </c>
+      <c r="R8" t="str">
+        <f>medium!R8</f>
+        <v>DNF</v>
+      </c>
+      <c r="S8" t="b">
+        <f>medium!U31</f>
+        <v>1</v>
+      </c>
+      <c r="T8" t="str">
+        <f>medium!S8</f>
+        <v>DNF</v>
+      </c>
+      <c r="U8" t="b">
+        <f>medium!V31</f>
+        <v>1</v>
+      </c>
+      <c r="W8" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X8" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y8" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC8" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD8" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>5.6078174756719097</v>
+      </c>
+      <c r="C9" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0.98667774354475302</v>
+      </c>
+      <c r="G9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>5.1470479866022725</v>
+      </c>
+      <c r="J9" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>122</v>
+      </c>
+      <c r="L9" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0.95371694147683095</v>
+      </c>
+      <c r="N9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="str">
+        <f>medium!Q9</f>
+        <v>DNF</v>
+      </c>
+      <c r="Q9" t="b">
+        <f>medium!T32</f>
+        <v>1</v>
+      </c>
+      <c r="R9" t="str">
+        <f>medium!R9</f>
+        <v>DNF</v>
+      </c>
+      <c r="S9" t="b">
+        <f>medium!U32</f>
+        <v>1</v>
+      </c>
+      <c r="T9" t="str">
+        <f>medium!S9</f>
+        <v>DNF</v>
+      </c>
+      <c r="U9" t="b">
+        <f>medium!V32</f>
+        <v>1</v>
+      </c>
+      <c r="W9" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y9" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC9" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="AD9" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10">
+        <v>9.1653420380357602</v>
+      </c>
+      <c r="C10" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2592.26979846721</v>
+      </c>
+      <c r="E10" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1.11382344592677</v>
+      </c>
+      <c r="G10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>8.3276917068090075</v>
+      </c>
+      <c r="J10" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>2380.075250618409</v>
+      </c>
+      <c r="L10" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1.0634032027079807</v>
+      </c>
+      <c r="N10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="str">
+        <f>medium!Q10</f>
+        <v>DNF</v>
+      </c>
+      <c r="Q10" t="b">
+        <f>medium!T33</f>
+        <v>1</v>
+      </c>
+      <c r="R10" t="str">
+        <f>medium!R10</f>
+        <v>DNF</v>
+      </c>
+      <c r="S10" t="b">
+        <f>medium!U33</f>
+        <v>1</v>
+      </c>
+      <c r="T10" t="str">
+        <f>medium!S10</f>
+        <v>DNF</v>
+      </c>
+      <c r="U10" t="b">
+        <f>medium!V33</f>
+        <v>1</v>
+      </c>
+      <c r="W10" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X10" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y10" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC10" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD10" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1.02696837260976</v>
+      </c>
+      <c r="G11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>122</v>
+      </c>
+      <c r="L11" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1.0066491204321186</v>
+      </c>
+      <c r="N11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="str">
+        <f>medium!Q11</f>
+        <v>DNF</v>
+      </c>
+      <c r="Q11" t="b">
+        <f>medium!T34</f>
+        <v>1</v>
+      </c>
+      <c r="R11" t="str">
+        <f>medium!R11</f>
+        <v>DNF</v>
+      </c>
+      <c r="S11" t="b">
+        <f>medium!U34</f>
+        <v>1</v>
+      </c>
+      <c r="T11" t="str">
+        <f>medium!S11</f>
+        <v>DNF</v>
+      </c>
+      <c r="U11" t="b">
+        <f>medium!V34</f>
+        <v>1</v>
+      </c>
+      <c r="W11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="X11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y11" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="8" t="str">
         <f t="shared" si="3"/>
         <v>Both DNF</v>
       </c>
-      <c r="S7" s="4" t="e">
+      <c r="AC11" s="8" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="8" t="e">
+        <v>Both DNF</v>
+      </c>
+      <c r="AD11" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W7" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X7" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8">
-        <v>2.51048566916386</v>
-      </c>
-      <c r="C8">
-        <v>51.666345031458803</v>
-      </c>
-      <c r="D8">
-        <v>1.0305372753522599</v>
-      </c>
-      <c r="G8">
-        <v>2.5325725846173173</v>
-      </c>
-      <c r="H8">
-        <v>48.818683080503398</v>
-      </c>
-      <c r="I8">
-        <v>0.9636110000033058</v>
-      </c>
-      <c r="L8" t="str">
-        <f>medium!Q8</f>
-        <v>DNF</v>
-      </c>
-      <c r="M8" t="str">
-        <f>medium!R8</f>
-        <v>DNF</v>
-      </c>
-      <c r="N8" t="str">
-        <f>medium!S8</f>
-        <v>DNF</v>
-      </c>
-      <c r="Q8" s="4" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R8" s="4" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S8" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="8" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W8" s="8" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X8" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>5.6078174756719097</v>
-      </c>
-      <c r="C9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9">
-        <v>0.98667774354475302</v>
-      </c>
-      <c r="G9">
-        <v>5.1470479866022725</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9">
-        <v>0.95371694147683095</v>
-      </c>
-      <c r="L9" t="str">
-        <f>medium!Q9</f>
-        <v>DNF</v>
-      </c>
-      <c r="M9" t="str">
-        <f>medium!R9</f>
-        <v>DNF</v>
-      </c>
-      <c r="N9" t="str">
-        <f>medium!S9</f>
-        <v>DNF</v>
-      </c>
-      <c r="Q9" s="4" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R9" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="S9" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="8" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W9" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X9" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10">
-        <v>9.1653420380357602</v>
-      </c>
-      <c r="C10">
-        <v>2592.26979846721</v>
-      </c>
-      <c r="D10">
-        <v>1.11382344592677</v>
-      </c>
-      <c r="G10">
-        <v>8.3276917068090075</v>
-      </c>
-      <c r="H10">
-        <v>2380.075250618409</v>
-      </c>
-      <c r="I10">
-        <v>1.0634032027079807</v>
-      </c>
-      <c r="L10" t="str">
-        <f>medium!Q10</f>
-        <v>DNF</v>
-      </c>
-      <c r="M10" t="str">
-        <f>medium!R10</f>
-        <v>DNF</v>
-      </c>
-      <c r="N10" t="str">
-        <f>medium!S10</f>
-        <v>DNF</v>
-      </c>
-      <c r="Q10" s="4" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R10" s="4" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S10" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="8" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W10" s="8" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X10" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11">
-        <v>1.02696837260976</v>
-      </c>
-      <c r="G11" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I11">
-        <v>1.0066491204321186</v>
-      </c>
-      <c r="L11" t="str">
-        <f>medium!Q11</f>
-        <v>DNF</v>
-      </c>
-      <c r="M11" t="str">
-        <f>medium!R11</f>
-        <v>DNF</v>
-      </c>
-      <c r="N11" t="str">
-        <f>medium!S11</f>
-        <v>DNF</v>
-      </c>
-      <c r="Q11" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="R11" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="S11" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="8" t="str">
-        <f t="shared" si="5"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="W11" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X11" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B12">
         <v>16.200210649062399</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>122</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12">
         <v>1.0002256954240301</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>14.93821258478857</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
         <v>122</v>
       </c>
-      <c r="I12">
+      <c r="L12" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12">
         <v>0.95663154856400634</v>
       </c>
-      <c r="L12" t="str">
+      <c r="N12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="str">
         <f>medium!Q12</f>
         <v>DNF</v>
       </c>
-      <c r="M12" t="str">
+      <c r="Q12" t="b">
+        <f>medium!T35</f>
+        <v>1</v>
+      </c>
+      <c r="R12" t="str">
         <f>medium!R12</f>
         <v>DNF</v>
       </c>
-      <c r="N12" t="str">
+      <c r="S12" t="b">
+        <f>medium!U35</f>
+        <v>1</v>
+      </c>
+      <c r="T12" t="str">
         <f>medium!S12</f>
         <v>DNF</v>
       </c>
-      <c r="Q12" s="4" t="e">
+      <c r="U12" t="b">
+        <f>medium!V35</f>
+        <v>1</v>
+      </c>
+      <c r="W12" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y12" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R12" s="4" t="str">
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="8" t="e">
         <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC12" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="S12" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="8" t="e">
+      <c r="AD12" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W12" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X12" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B13">
         <v>5.3246647516935202</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>122</v>
       </c>
-      <c r="D13">
+      <c r="E13" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13">
         <v>0.98622140980937301</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>5.893439298108559</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>122</v>
       </c>
-      <c r="I13">
+      <c r="L13" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13">
         <v>1.0383846881901357</v>
       </c>
-      <c r="L13" t="str">
+      <c r="N13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="str">
         <f>medium!Q13</f>
         <v>DNF</v>
       </c>
-      <c r="M13" t="str">
+      <c r="Q13" t="b">
+        <f>medium!T36</f>
+        <v>1</v>
+      </c>
+      <c r="R13" t="str">
         <f>medium!R13</f>
         <v>DNF</v>
       </c>
-      <c r="N13" t="str">
+      <c r="S13" t="b">
+        <f>medium!U36</f>
+        <v>1</v>
+      </c>
+      <c r="T13" t="str">
         <f>medium!S13</f>
         <v>DNF</v>
       </c>
-      <c r="Q13" s="4" t="e">
+      <c r="U13" t="b">
+        <f>medium!V36</f>
+        <v>1</v>
+      </c>
+      <c r="W13" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y13" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R13" s="4" t="str">
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="8" t="e">
         <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC13" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="S13" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="8" t="e">
+      <c r="AD13" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W13" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X13" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B14">
         <v>6.97379039331953</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>122</v>
       </c>
-      <c r="D14">
+      <c r="E14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14">
         <v>0.93230646877887302</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>7.1658105337419258</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
         <v>122</v>
       </c>
-      <c r="I14">
+      <c r="L14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14">
         <v>0.9622125708238719</v>
       </c>
-      <c r="L14" t="str">
+      <c r="N14" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="str">
         <f>medium!Q14</f>
         <v>DNF</v>
       </c>
-      <c r="M14" t="str">
+      <c r="Q14" t="b">
+        <f>medium!T37</f>
+        <v>1</v>
+      </c>
+      <c r="R14" t="str">
         <f>medium!R14</f>
         <v>DNF</v>
       </c>
-      <c r="N14" t="str">
+      <c r="S14" t="b">
+        <f>medium!U37</f>
+        <v>1</v>
+      </c>
+      <c r="T14" t="str">
         <f>medium!S14</f>
         <v>DNF</v>
       </c>
-      <c r="Q14" s="4" t="e">
+      <c r="U14" t="b">
+        <f>medium!V37</f>
+        <v>1</v>
+      </c>
+      <c r="W14" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y14" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R14" s="4" t="str">
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="8" t="e">
         <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC14" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="S14" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="8" t="e">
+      <c r="AD14" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W14" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X14" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B15">
         <v>16.491917076943398</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
         <v>122</v>
       </c>
-      <c r="D15">
+      <c r="E15" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15">
         <v>0.93431799747231803</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>16.019783167542194</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
         <v>122</v>
       </c>
-      <c r="I15">
+      <c r="L15" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15">
         <v>0.96663686151782724</v>
       </c>
-      <c r="L15" t="str">
+      <c r="N15" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="str">
         <f>medium!Q15</f>
         <v>DNF</v>
       </c>
-      <c r="M15" t="str">
+      <c r="Q15" t="b">
+        <f>medium!T38</f>
+        <v>1</v>
+      </c>
+      <c r="R15" t="str">
         <f>medium!R15</f>
         <v>DNF</v>
       </c>
-      <c r="N15" t="str">
+      <c r="S15" t="b">
+        <f>medium!U38</f>
+        <v>1</v>
+      </c>
+      <c r="T15" t="str">
         <f>medium!S15</f>
         <v>DNF</v>
       </c>
-      <c r="Q15" s="4" t="e">
+      <c r="U15" t="b">
+        <f>medium!V38</f>
+        <v>1</v>
+      </c>
+      <c r="W15" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y15" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R15" s="4" t="str">
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="8" t="e">
         <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC15" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="S15" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="8" t="e">
+      <c r="AD15" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W15" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X15" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B16">
         <v>6.0146968350536598</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16">
         <v>17.8318750427234</v>
       </c>
-      <c r="D16">
+      <c r="E16" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16">
         <v>0.91482671406111205</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>5.4918166660995613</v>
       </c>
-      <c r="H16">
+      <c r="J16" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16">
         <v>17.443499268433769</v>
       </c>
-      <c r="I16">
+      <c r="L16" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16">
         <v>0.93436319711456661</v>
       </c>
-      <c r="L16" t="str">
+      <c r="N16" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="str">
         <f>medium!Q16</f>
         <v>DNF</v>
       </c>
-      <c r="M16" t="str">
+      <c r="Q16" t="b">
+        <f>medium!T39</f>
+        <v>1</v>
+      </c>
+      <c r="R16" t="str">
         <f>medium!R16</f>
         <v>DNF</v>
       </c>
-      <c r="N16" t="str">
+      <c r="S16" t="b">
+        <f>medium!U39</f>
+        <v>1</v>
+      </c>
+      <c r="T16" t="str">
         <f>medium!S16</f>
         <v>DNF</v>
       </c>
-      <c r="Q16" s="4" t="e">
+      <c r="U16" t="b">
+        <f>medium!V39</f>
+        <v>1</v>
+      </c>
+      <c r="W16" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X16" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y16" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R16" s="4" t="e">
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="8" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S16" s="4" t="e">
+      <c r="AC16" s="8" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="8" t="e">
+      <c r="AD16" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W16" s="8" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X16" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B17">
         <v>3.5213202715336802</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <v>13.660013820576401</v>
       </c>
-      <c r="D17">
+      <c r="E17" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17">
         <v>0.77045648550871904</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>3.5535822495688247</v>
       </c>
-      <c r="H17">
+      <c r="J17" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17">
         <v>17.006758961450615</v>
       </c>
-      <c r="I17">
+      <c r="L17" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17">
         <v>0.86342236517037252</v>
       </c>
-      <c r="L17" t="str">
+      <c r="N17" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="str">
         <f>medium!Q17</f>
         <v>DNF</v>
       </c>
-      <c r="M17" t="str">
+      <c r="Q17" t="b">
+        <f>medium!T40</f>
+        <v>1</v>
+      </c>
+      <c r="R17" t="str">
         <f>medium!R17</f>
         <v>DNF</v>
       </c>
-      <c r="N17" t="str">
+      <c r="S17" t="b">
+        <f>medium!U40</f>
+        <v>1</v>
+      </c>
+      <c r="T17" t="str">
         <f>medium!S17</f>
         <v>DNF</v>
       </c>
-      <c r="Q17" s="4" t="e">
+      <c r="U17" t="b">
+        <f>medium!V40</f>
+        <v>1</v>
+      </c>
+      <c r="W17" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X17" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y17" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R17" s="4" t="e">
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="8" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S17" s="4" t="e">
+      <c r="AC17" s="8" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="8" t="e">
+      <c r="AD17" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W17" s="8" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X17" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B18">
         <v>22.078011868866302</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
         <v>122</v>
       </c>
-      <c r="D18">
+      <c r="E18" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18">
         <v>0.98670994257619704</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>20.514766688646677</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
         <v>122</v>
       </c>
-      <c r="I18">
+      <c r="L18" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18">
         <v>1.0183158139715294</v>
       </c>
-      <c r="L18" t="str">
+      <c r="N18" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="str">
         <f>medium!Q18</f>
         <v>DNF</v>
       </c>
-      <c r="M18" t="str">
+      <c r="Q18" t="b">
+        <f>medium!T41</f>
+        <v>1</v>
+      </c>
+      <c r="R18" t="str">
         <f>medium!R18</f>
         <v>DNF</v>
       </c>
-      <c r="N18" t="str">
+      <c r="S18" t="b">
+        <f>medium!U41</f>
+        <v>1</v>
+      </c>
+      <c r="T18" t="str">
         <f>medium!S18</f>
         <v>DNF</v>
       </c>
-      <c r="Q18" s="4" t="e">
+      <c r="U18" t="b">
+        <f>medium!V41</f>
+        <v>1</v>
+      </c>
+      <c r="W18" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Both DNF</v>
+      </c>
+      <c r="Y18" s="4" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R18" s="4" t="str">
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="8" t="e">
         <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC18" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="S18" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="8" t="e">
+      <c r="AD18" s="8" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W18" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>Both DNF</v>
-      </c>
-      <c r="X18" s="8" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="8"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="8"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8"/>
+      <c r="AD20" s="8"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="3" t="s">
         <v>126</v>
@@ -4485,1065 +5533,1575 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="L21" s="3" t="s">
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="P21" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="8"/>
+      <c r="Q21" s="3"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="8"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="J22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="L22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="L22" s="3" t="s">
+      <c r="N22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="Q22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="R22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="S22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="T22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="Q22" s="6" t="s">
+      <c r="U22" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="W22" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="R22" s="6" t="s">
+      <c r="X22" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="S22" s="6" t="s">
+      <c r="Y22" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="7" t="s">
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
+      <c r="AB22" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="W22" s="7" t="s">
+      <c r="AC22" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X22" s="7" t="s">
+      <c r="AD22" s="7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B23" t="s">
         <v>122</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
         <v>122</v>
       </c>
-      <c r="D23">
+      <c r="E23" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23">
         <v>0.99888858359393196</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
         <v>122</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
         <v>122</v>
       </c>
-      <c r="I23">
+      <c r="L23" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23">
         <v>0.99637978350764578</v>
       </c>
-      <c r="L23" t="str">
+      <c r="N23" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="str">
         <f>large!Q3</f>
         <v>DNF</v>
       </c>
-      <c r="M23" t="str">
+      <c r="Q23" t="b">
+        <f>large!T26</f>
+        <v>1</v>
+      </c>
+      <c r="R23" t="str">
         <f>large!R3</f>
         <v>DNF</v>
       </c>
-      <c r="N23" t="str">
+      <c r="S23" t="b">
+        <f>large!U26</f>
+        <v>1</v>
+      </c>
+      <c r="T23" t="str">
         <f>large!S3</f>
         <v>DNF</v>
       </c>
-      <c r="Q23" s="4" t="str">
-        <f>IF(AND(L23="DNF", B23="DNF"), "Both DNF",B23/ L23)</f>
+      <c r="U23" t="b">
+        <f>large!V26</f>
+        <v>1</v>
+      </c>
+      <c r="W23" s="4" t="str">
+        <f t="shared" si="0"/>
         <v>Both DNF</v>
       </c>
-      <c r="R23" s="4" t="str">
-        <f t="shared" ref="R23:S23" si="8">IF(AND(M23="DNF", C23="DNF"), "Both DNF",C23/ M23)</f>
+      <c r="X23" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S23" s="4" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="8" t="str">
-        <f>IF(AND(L23="DNF", G23="DNF"), "Both DNF",G23/ L23)</f>
+      <c r="Y23" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="8" t="str">
+        <f t="shared" si="3"/>
         <v>Both DNF</v>
       </c>
-      <c r="W23" s="8" t="str">
-        <f t="shared" ref="W23:X23" si="9">IF(AND(M23="DNF", H23="DNF"), "Both DNF",H23/ M23)</f>
+      <c r="AC23" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X23" s="8" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD23" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B24">
         <v>5.9046005191808497</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24">
         <v>1019.28252091145</v>
       </c>
-      <c r="D24">
+      <c r="E24" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24">
         <v>0.90301413325641799</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>5.2713685309989806</v>
       </c>
-      <c r="H24">
+      <c r="J24" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24">
         <v>773.24689761508046</v>
       </c>
-      <c r="I24">
+      <c r="L24" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24">
         <v>0.97403695506204779</v>
       </c>
-      <c r="L24" t="str">
+      <c r="N24" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="str">
         <f>large!Q4</f>
         <v>DNF</v>
       </c>
-      <c r="M24" t="str">
+      <c r="Q24" t="b">
+        <f>large!T27</f>
+        <v>1</v>
+      </c>
+      <c r="R24" t="str">
         <f>large!R4</f>
         <v>DNF</v>
       </c>
-      <c r="N24" t="str">
+      <c r="S24" t="b">
+        <f>large!U27</f>
+        <v>1</v>
+      </c>
+      <c r="T24" t="str">
         <f>large!S4</f>
         <v>DNF</v>
       </c>
-      <c r="Q24" s="4" t="e">
-        <f t="shared" ref="Q24:Q38" si="10">IF(AND(L24="DNF", B24="DNF"), "Both DNF",B24/ L24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R24" s="4" t="e">
-        <f t="shared" ref="R24:R38" si="11">IF(AND(M24="DNF", C24="DNF"), "Both DNF",C24/ M24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S24" s="4" t="e">
-        <f t="shared" ref="S24:S38" si="12">IF(AND(N24="DNF", D24="DNF"), "Both DNF",D24/ N24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="8" t="e">
-        <f t="shared" ref="V24:V38" si="13">IF(AND(L24="DNF", G24="DNF"), "Both DNF",G24/ L24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W24" s="8" t="e">
-        <f t="shared" ref="W24:W38" si="14">IF(AND(M24="DNF", H24="DNF"), "Both DNF",H24/ M24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X24" s="8" t="e">
-        <f t="shared" ref="X24:X38" si="15">IF(AND(N24="DNF", I24="DNF"), "Both DNF",I24/ N24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U24" t="b">
+        <f>large!V27</f>
+        <v>1</v>
+      </c>
+      <c r="W24" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X24" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y24" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC24" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD24" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B25">
         <v>3.4898416052724301</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
         <v>122</v>
       </c>
-      <c r="D25">
+      <c r="E25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25">
         <v>0.97534098529915503</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>3.8140979194700342</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
         <v>122</v>
       </c>
-      <c r="I25">
+      <c r="L25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25">
         <v>1.0253941965980058</v>
       </c>
-      <c r="L25" t="str">
+      <c r="N25" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="str">
         <f>large!Q5</f>
         <v>DNF</v>
       </c>
-      <c r="M25" t="str">
+      <c r="Q25" t="b">
+        <f>large!T28</f>
+        <v>1</v>
+      </c>
+      <c r="R25" t="str">
         <f>large!R5</f>
         <v>DNF</v>
       </c>
-      <c r="N25" t="str">
+      <c r="S25" t="b">
+        <f>large!U28</f>
+        <v>1</v>
+      </c>
+      <c r="T25" t="str">
         <f>large!S5</f>
         <v>DNF</v>
       </c>
-      <c r="Q25" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R25" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U25" t="b">
+        <f>large!V28</f>
+        <v>1</v>
+      </c>
+      <c r="W25" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X25" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S25" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W25" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="Y25" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC25" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X25" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD25" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B26">
         <v>7.65181702519945</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>122</v>
       </c>
-      <c r="D26">
+      <c r="E26" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26">
         <v>0.98945606320030699</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>6.8397003847918674</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="s">
         <v>122</v>
       </c>
-      <c r="I26">
+      <c r="L26" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26">
         <v>1.0038987937709309</v>
       </c>
-      <c r="L26" t="str">
+      <c r="N26" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="str">
         <f>large!Q6</f>
         <v>DNF</v>
       </c>
-      <c r="M26" t="str">
+      <c r="Q26" t="b">
+        <f>large!T29</f>
+        <v>1</v>
+      </c>
+      <c r="R26" t="str">
         <f>large!R6</f>
         <v>DNF</v>
       </c>
-      <c r="N26" t="str">
+      <c r="S26" t="b">
+        <f>large!U29</f>
+        <v>1</v>
+      </c>
+      <c r="T26" t="str">
         <f>large!S6</f>
         <v>DNF</v>
       </c>
-      <c r="Q26" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R26" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U26" t="b">
+        <f>large!V29</f>
+        <v>1</v>
+      </c>
+      <c r="W26" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X26" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S26" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W26" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="Y26" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC26" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X26" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD26" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B27">
         <v>3.7135821544106999</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
         <v>122</v>
       </c>
-      <c r="D27">
+      <c r="E27" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27">
         <v>0.925257109748443</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>2.467324144486692</v>
       </c>
-      <c r="H27" t="s">
+      <c r="J27" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
         <v>122</v>
       </c>
-      <c r="I27">
+      <c r="L27" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27">
         <v>0.77978453738910014</v>
       </c>
-      <c r="L27" t="str">
+      <c r="N27" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="str">
         <f>large!Q7</f>
         <v>DNF</v>
       </c>
-      <c r="M27" t="str">
+      <c r="Q27" t="b">
+        <f>large!T30</f>
+        <v>1</v>
+      </c>
+      <c r="R27" t="str">
         <f>large!R7</f>
         <v>DNF</v>
       </c>
-      <c r="N27" t="str">
+      <c r="S27" t="b">
+        <f>large!U30</f>
+        <v>1</v>
+      </c>
+      <c r="T27" t="str">
         <f>large!S7</f>
         <v>DNF</v>
       </c>
-      <c r="Q27" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R27" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U27" t="b">
+        <f>large!V30</f>
+        <v>1</v>
+      </c>
+      <c r="W27" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X27" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S27" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W27" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="Y27" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC27" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X27" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD27" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B28">
         <v>1.10557835186714</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28">
         <v>51.2885810712378</v>
       </c>
-      <c r="D28">
+      <c r="E28" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28">
         <v>0.97694119360947895</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>1.2417965273701552</v>
       </c>
-      <c r="H28">
+      <c r="J28" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28">
         <v>45.851747811009737</v>
       </c>
-      <c r="I28">
+      <c r="L28" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28">
         <v>0.93933717618227108</v>
       </c>
-      <c r="L28" t="str">
+      <c r="N28" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="str">
         <f>large!Q8</f>
         <v>DNF</v>
       </c>
-      <c r="M28" t="str">
+      <c r="Q28" t="b">
+        <f>large!T31</f>
+        <v>1</v>
+      </c>
+      <c r="R28" t="str">
         <f>large!R8</f>
         <v>DNF</v>
       </c>
-      <c r="N28" t="str">
+      <c r="S28" t="b">
+        <f>large!U31</f>
+        <v>1</v>
+      </c>
+      <c r="T28" t="str">
         <f>large!S8</f>
         <v>DNF</v>
       </c>
-      <c r="Q28" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R28" s="4" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S28" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W28" s="8" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X28" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U28" t="b">
+        <f>large!V31</f>
+        <v>1</v>
+      </c>
+      <c r="W28" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X28" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y28" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC28" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD28" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B29">
         <v>9.8081843382431906</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
         <v>122</v>
       </c>
-      <c r="D29">
+      <c r="E29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29">
         <v>0.993683150594314</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29">
         <v>9.8133638792978353</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
         <v>122</v>
       </c>
-      <c r="I29">
+      <c r="L29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29">
         <v>0.9993951154426044</v>
       </c>
-      <c r="L29" t="str">
+      <c r="N29" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="str">
         <f>large!Q9</f>
         <v>DNF</v>
       </c>
-      <c r="M29" t="str">
+      <c r="Q29" t="b">
+        <f>large!T32</f>
+        <v>1</v>
+      </c>
+      <c r="R29" t="str">
         <f>large!R9</f>
         <v>DNF</v>
       </c>
-      <c r="N29" t="str">
+      <c r="S29" t="b">
+        <f>large!U32</f>
+        <v>1</v>
+      </c>
+      <c r="T29" t="str">
         <f>large!S9</f>
         <v>DNF</v>
       </c>
-      <c r="Q29" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R29" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U29" t="b">
+        <f>large!V32</f>
+        <v>1</v>
+      </c>
+      <c r="W29" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X29" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S29" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W29" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="Y29" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC29" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X29" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD29" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B30">
         <v>11.024187577128799</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30">
         <v>21897.751871657802</v>
       </c>
-      <c r="D30">
+      <c r="E30" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30">
         <v>0.93245577951460301</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>10.709161931818182</v>
       </c>
-      <c r="H30">
+      <c r="J30" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30">
         <v>18723.854758522728</v>
       </c>
-      <c r="I30">
+      <c r="L30" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30">
         <v>0.9118430397727274</v>
       </c>
-      <c r="L30" t="str">
+      <c r="N30" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="str">
         <f>large!Q10</f>
         <v>DNF</v>
       </c>
-      <c r="M30" t="str">
+      <c r="Q30" t="b">
+        <f>large!T33</f>
+        <v>1</v>
+      </c>
+      <c r="R30" t="str">
         <f>large!R10</f>
         <v>DNF</v>
       </c>
-      <c r="N30" t="str">
+      <c r="S30" t="b">
+        <f>large!U33</f>
+        <v>1</v>
+      </c>
+      <c r="T30" t="str">
         <f>large!S10</f>
         <v>DNF</v>
       </c>
-      <c r="Q30" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R30" s="4" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S30" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W30" s="8" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X30" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U30" t="b">
+        <f>large!V33</f>
+        <v>1</v>
+      </c>
+      <c r="W30" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X30" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y30" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC30" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD30" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B31" t="s">
         <v>122</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
         <v>122</v>
       </c>
-      <c r="D31">
+      <c r="E31" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31">
         <v>1.0419824376642399</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
         <v>122</v>
       </c>
-      <c r="H31" t="s">
+      <c r="J31" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
         <v>122</v>
       </c>
-      <c r="I31">
+      <c r="L31" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31">
         <v>0.98907127490255986</v>
       </c>
-      <c r="L31" t="str">
+      <c r="N31" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="str">
         <f>large!Q11</f>
         <v>DNF</v>
       </c>
-      <c r="M31" t="str">
+      <c r="Q31" t="b">
+        <f>large!T34</f>
+        <v>1</v>
+      </c>
+      <c r="R31" t="str">
         <f>large!R11</f>
         <v>DNF</v>
       </c>
-      <c r="N31" t="str">
+      <c r="S31" t="b">
+        <f>large!U34</f>
+        <v>1</v>
+      </c>
+      <c r="T31" t="str">
         <f>large!S11</f>
         <v>DNF</v>
       </c>
-      <c r="Q31" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="U31" t="b">
+        <f>large!V34</f>
+        <v>1</v>
+      </c>
+      <c r="W31" s="4" t="str">
+        <f t="shared" si="0"/>
         <v>Both DNF</v>
       </c>
-      <c r="R31" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="X31" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S31" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="8" t="str">
-        <f t="shared" si="13"/>
+      <c r="Y31" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
+      <c r="AB31" s="8" t="str">
+        <f t="shared" si="3"/>
         <v>Both DNF</v>
       </c>
-      <c r="W31" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="AC31" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X31" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD31" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B32" t="s">
         <v>122</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
         <v>122</v>
       </c>
-      <c r="D32">
+      <c r="E32" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32">
         <v>0.98538629775745301</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
         <v>122</v>
       </c>
-      <c r="H32" t="s">
+      <c r="J32" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
         <v>122</v>
       </c>
-      <c r="I32">
+      <c r="L32" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32">
         <v>0.99774547736066088</v>
       </c>
-      <c r="L32" t="str">
+      <c r="N32" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="str">
         <f>large!Q12</f>
         <v>DNF</v>
       </c>
-      <c r="M32" t="str">
+      <c r="Q32" t="b">
+        <f>large!T35</f>
+        <v>1</v>
+      </c>
+      <c r="R32" t="str">
         <f>large!R12</f>
         <v>DNF</v>
       </c>
-      <c r="N32" t="str">
+      <c r="S32" t="b">
+        <f>large!U35</f>
+        <v>1</v>
+      </c>
+      <c r="T32" t="str">
         <f>large!S12</f>
         <v>DNF</v>
       </c>
-      <c r="Q32" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="U32" t="b">
+        <f>large!V35</f>
+        <v>1</v>
+      </c>
+      <c r="W32" s="4" t="str">
+        <f t="shared" si="0"/>
         <v>Both DNF</v>
       </c>
-      <c r="R32" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="X32" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S32" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="8" t="str">
-        <f t="shared" si="13"/>
+      <c r="Y32" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="8" t="str">
+        <f t="shared" si="3"/>
         <v>Both DNF</v>
       </c>
-      <c r="W32" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="AC32" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X32" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD32" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B33">
         <v>1.3858971656903301</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
         <v>122</v>
       </c>
-      <c r="D33">
+      <c r="E33" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33">
         <v>1.0046483025034401</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33">
         <v>1.0144915431787682</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
         <v>122</v>
       </c>
-      <c r="I33">
+      <c r="L33" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33">
         <v>1.0094519911892776</v>
       </c>
-      <c r="L33" t="str">
+      <c r="N33" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="str">
         <f>large!Q13</f>
         <v>DNF</v>
       </c>
-      <c r="M33" t="str">
+      <c r="Q33" t="b">
+        <f>large!T36</f>
+        <v>1</v>
+      </c>
+      <c r="R33" t="str">
         <f>large!R13</f>
         <v>DNF</v>
       </c>
-      <c r="N33" t="str">
+      <c r="S33" t="b">
+        <f>large!U36</f>
+        <v>1</v>
+      </c>
+      <c r="T33" t="str">
         <f>large!S13</f>
         <v>DNF</v>
       </c>
-      <c r="Q33" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R33" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U33" t="b">
+        <f>large!V36</f>
+        <v>1</v>
+      </c>
+      <c r="W33" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X33" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S33" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W33" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="Y33" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC33" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X33" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD33" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B34">
         <v>3.53580108138594</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
         <v>122</v>
       </c>
-      <c r="D34">
+      <c r="E34" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34">
         <v>1.0203469756639201</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>3.8578670960294628</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="s">
         <v>122</v>
       </c>
-      <c r="I34">
+      <c r="L34" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34">
         <v>0.99167231617714413</v>
       </c>
-      <c r="L34" t="str">
+      <c r="N34" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="str">
         <f>large!Q14</f>
         <v>DNF</v>
       </c>
-      <c r="M34" t="str">
+      <c r="Q34" t="b">
+        <f>large!T37</f>
+        <v>1</v>
+      </c>
+      <c r="R34" t="str">
         <f>large!R14</f>
         <v>DNF</v>
       </c>
-      <c r="N34" t="str">
+      <c r="S34" t="b">
+        <f>large!U37</f>
+        <v>1</v>
+      </c>
+      <c r="T34" t="str">
         <f>large!S14</f>
         <v>DNF</v>
       </c>
-      <c r="Q34" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R34" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U34" t="b">
+        <f>large!V37</f>
+        <v>1</v>
+      </c>
+      <c r="W34" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X34" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S34" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W34" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="Y34" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC34" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X34" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD34" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B35" t="s">
         <v>122</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
         <v>122</v>
       </c>
-      <c r="D35">
+      <c r="E35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35">
         <v>0.97039063577748796</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
         <v>122</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="s">
         <v>122</v>
       </c>
-      <c r="I35">
+      <c r="L35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35">
         <v>0.96530797370507559</v>
       </c>
-      <c r="L35" t="str">
+      <c r="N35" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="str">
         <f>large!Q15</f>
         <v>DNF</v>
       </c>
-      <c r="M35" t="str">
+      <c r="Q35" t="b">
+        <f>large!T38</f>
+        <v>1</v>
+      </c>
+      <c r="R35" t="str">
         <f>large!R15</f>
         <v>DNF</v>
       </c>
-      <c r="N35" t="str">
+      <c r="S35" t="b">
+        <f>large!U38</f>
+        <v>1</v>
+      </c>
+      <c r="T35" t="str">
         <f>large!S15</f>
         <v>DNF</v>
       </c>
-      <c r="Q35" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="U35" t="b">
+        <f>large!V38</f>
+        <v>1</v>
+      </c>
+      <c r="W35" s="4" t="str">
+        <f t="shared" si="0"/>
         <v>Both DNF</v>
       </c>
-      <c r="R35" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="X35" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S35" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="8" t="str">
-        <f t="shared" si="13"/>
+      <c r="Y35" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="4"/>
+      <c r="AB35" s="8" t="str">
+        <f t="shared" si="3"/>
         <v>Both DNF</v>
       </c>
-      <c r="W35" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="AC35" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X35" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD35" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B36">
         <v>15.913490642537701</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36">
         <v>1762.88766228031</v>
       </c>
-      <c r="D36">
+      <c r="E36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36">
         <v>1.00549163809784</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36">
         <v>10.247392176239764</v>
       </c>
-      <c r="H36">
+      <c r="J36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36">
         <v>924.98827418413407</v>
       </c>
-      <c r="I36">
+      <c r="L36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36">
         <v>0.99303617145466005</v>
       </c>
-      <c r="L36" t="str">
+      <c r="N36" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="str">
         <f>large!Q16</f>
         <v>DNF</v>
       </c>
-      <c r="M36" t="str">
+      <c r="Q36" t="b">
+        <f>large!T39</f>
+        <v>1</v>
+      </c>
+      <c r="R36" t="str">
         <f>large!R16</f>
         <v>DNF</v>
       </c>
-      <c r="N36" t="str">
+      <c r="S36" t="b">
+        <f>large!U39</f>
+        <v>1</v>
+      </c>
+      <c r="T36" t="str">
         <f>large!S16</f>
         <v>DNF</v>
       </c>
-      <c r="Q36" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R36" s="4" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S36" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W36" s="8" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X36" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U36" t="b">
+        <f>large!V39</f>
+        <v>1</v>
+      </c>
+      <c r="W36" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X36" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y36" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
+      <c r="AB36" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC36" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD36" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B37">
         <v>4.4974960652453904</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37">
         <v>98.448347403062002</v>
       </c>
-      <c r="D37">
+      <c r="E37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37">
         <v>0.95398483330948602</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37">
         <v>3.5433877681716299</v>
       </c>
-      <c r="H37">
+      <c r="J37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37">
         <v>89.979303117631645</v>
       </c>
-      <c r="I37">
+      <c r="L37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37">
         <v>0.94651122172736013</v>
       </c>
-      <c r="L37" t="str">
+      <c r="N37" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="str">
         <f>large!Q17</f>
         <v>DNF</v>
       </c>
-      <c r="M37" t="str">
+      <c r="Q37" t="b">
+        <f>large!T40</f>
+        <v>1</v>
+      </c>
+      <c r="R37" t="str">
         <f>large!R17</f>
         <v>DNF</v>
       </c>
-      <c r="N37" t="str">
+      <c r="S37" t="b">
+        <f>large!U40</f>
+        <v>1</v>
+      </c>
+      <c r="T37" t="str">
         <f>large!S17</f>
         <v>DNF</v>
       </c>
-      <c r="Q37" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R37" s="4" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S37" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W37" s="8" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X37" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U37" t="b">
+        <f>large!V40</f>
+        <v>1</v>
+      </c>
+      <c r="W37" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X37" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y37" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
+      <c r="AB37" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC37" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD37" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B38">
         <v>9.6127213802096101</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
         <v>122</v>
       </c>
-      <c r="D38">
+      <c r="E38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38">
         <v>0.97527108666722495</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38">
         <v>6.9205912416252673</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
         <v>122</v>
       </c>
-      <c r="I38">
+      <c r="L38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38">
         <v>1.0047135071439093</v>
       </c>
-      <c r="L38" t="str">
+      <c r="N38" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="str">
         <f>large!Q18</f>
         <v>DNF</v>
       </c>
-      <c r="M38" t="str">
+      <c r="Q38" t="b">
+        <f>large!T41</f>
+        <v>1</v>
+      </c>
+      <c r="R38" t="str">
         <f>large!R18</f>
         <v>DNF</v>
       </c>
-      <c r="N38" t="str">
+      <c r="S38" t="b">
+        <f>large!U41</f>
+        <v>1</v>
+      </c>
+      <c r="T38" t="str">
         <f>large!S18</f>
         <v>DNF</v>
       </c>
-      <c r="Q38" s="4" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R38" s="4" t="str">
-        <f t="shared" si="11"/>
+      <c r="U38" t="b">
+        <f>large!V41</f>
+        <v>1</v>
+      </c>
+      <c r="W38" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X38" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>Both DNF</v>
       </c>
-      <c r="S38" s="4" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="8" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W38" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="Y38" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC38" s="8" t="str">
+        <f t="shared" si="4"/>
         <v>Both DNF</v>
       </c>
-      <c r="X38" s="8" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="AD38" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="8"/>
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="8"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="8"/>
+      <c r="AC39" s="8"/>
+      <c r="AD39" s="8"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="3" t="s">
         <v>127</v>
@@ -5552,1056 +7110,1791 @@
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="G40" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="L40" s="3" t="s">
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="8"/>
+      <c r="Q40" s="3"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="8"/>
+      <c r="AC40" s="8"/>
+      <c r="AD40" s="8"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="L41" s="3" t="s">
+      <c r="J41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="P41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="Q41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="R41" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="N41" s="3" t="s">
+      <c r="S41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="T41" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="Q41" s="7" t="s">
+      <c r="U41" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="W41" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="R41" s="7" t="s">
+      <c r="X41" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="S41" s="7" t="s">
+      <c r="Y41" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="7" t="s">
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="W41" s="7" t="s">
+      <c r="AC41" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X41" s="7" t="s">
+      <c r="AD41" s="7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B42">
         <v>6.5003972457627102</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42">
         <v>0.184057203389831</v>
       </c>
-      <c r="D42">
+      <c r="E42" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42">
         <v>0.71106991525423702</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>6.1550941839681013</v>
       </c>
-      <c r="H42">
+      <c r="J42" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42">
         <v>0.19043035886154269</v>
       </c>
-      <c r="I42">
+      <c r="L42" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>0.78963288876667126</v>
       </c>
-      <c r="L42" t="str">
+      <c r="N42" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="str">
         <f>small!Q3</f>
         <v>DNF</v>
       </c>
-      <c r="M42" t="str">
+      <c r="Q42" t="b">
+        <f>small!T26</f>
+        <v>1</v>
+      </c>
+      <c r="R42" t="str">
         <f>small!R3</f>
         <v>DNF</v>
       </c>
-      <c r="N42" t="str">
+      <c r="S42" t="b">
+        <f>small!U26</f>
+        <v>1</v>
+      </c>
+      <c r="T42" t="str">
         <f>small!S3</f>
         <v>DNF</v>
       </c>
-      <c r="Q42" s="4" t="e">
-        <f>IF(AND(L42="DNF", B42="DNF"), "Both DNF",B42/ L42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R42" s="4" t="e">
-        <f t="shared" ref="R42:S42" si="16">IF(AND(M42="DNF", C42="DNF"), "Both DNF",C42/ M42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S42" s="4" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="8" t="e">
-        <f>IF(AND(L42="DNF", G42="DNF"), "Both DNF",G42/ L42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W42" s="8" t="e">
-        <f t="shared" ref="W42:X42" si="17">IF(AND(M42="DNF", H42="DNF"), "Both DNF",H42/ M42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X42" s="8" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U42" t="b">
+        <f>small!V26</f>
+        <v>1</v>
+      </c>
+      <c r="W42" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X42" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y42" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+      <c r="AB42" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC42" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD42" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B43">
         <v>4.0844673539518901</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43">
         <v>0.106460481099656</v>
       </c>
-      <c r="D43">
+      <c r="E43" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43">
         <v>0.73512027491408904</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43">
         <v>3.4646417025862069</v>
       </c>
-      <c r="H43">
+      <c r="J43" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43">
         <v>9.6982758620689655E-2</v>
       </c>
-      <c r="I43">
+      <c r="L43" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43">
         <v>0.9514412715517242</v>
       </c>
-      <c r="L43" t="str">
+      <c r="N43" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="str">
         <f>small!Q4</f>
         <v>DNF</v>
       </c>
-      <c r="M43" t="str">
+      <c r="Q43" t="b">
+        <f>small!T27</f>
+        <v>1</v>
+      </c>
+      <c r="R43" t="str">
         <f>small!R4</f>
         <v>DNF</v>
       </c>
-      <c r="N43" t="str">
+      <c r="S43" t="b">
+        <f>small!U27</f>
+        <v>1</v>
+      </c>
+      <c r="T43" t="str">
         <f>small!S4</f>
         <v>DNF</v>
       </c>
-      <c r="Q43" s="4" t="e">
-        <f t="shared" ref="Q43:Q57" si="18">IF(AND(L43="DNF", B43="DNF"), "Both DNF",B43/ L43)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R43" s="4" t="e">
-        <f t="shared" ref="R43:R57" si="19">IF(AND(M43="DNF", C43="DNF"), "Both DNF",C43/ M43)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S43" s="4" t="e">
-        <f t="shared" ref="S43:S57" si="20">IF(AND(N43="DNF", D43="DNF"), "Both DNF",D43/ N43)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="8" t="e">
-        <f t="shared" ref="V43:V57" si="21">IF(AND(L43="DNF", G43="DNF"), "Both DNF",G43/ L43)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W43" s="8" t="e">
-        <f t="shared" ref="W43:W57" si="22">IF(AND(M43="DNF", H43="DNF"), "Both DNF",H43/ M43)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X43" s="8" t="e">
-        <f t="shared" ref="X43:X57" si="23">IF(AND(N43="DNF", I43="DNF"), "Both DNF",I43/ N43)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U43" t="b">
+        <f>small!V27</f>
+        <v>1</v>
+      </c>
+      <c r="W43" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X43" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y43" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC43" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD43" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B44">
         <v>2.75648919473621</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44">
         <v>0.21592418205964001</v>
       </c>
-      <c r="D44">
+      <c r="E44" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44">
         <v>0.71912350597609598</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44">
         <v>3.1806377257011142</v>
       </c>
-      <c r="H44">
+      <c r="J44" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44">
         <v>0.27137917787168653</v>
       </c>
-      <c r="I44">
+      <c r="L44" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44">
         <v>0.75766423357664225</v>
       </c>
-      <c r="L44" t="str">
+      <c r="N44" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="str">
         <f>small!Q5</f>
         <v>DNF</v>
       </c>
-      <c r="M44" t="str">
+      <c r="Q44" t="b">
+        <f>small!T28</f>
+        <v>1</v>
+      </c>
+      <c r="R44" t="str">
         <f>small!R5</f>
         <v>DNF</v>
       </c>
-      <c r="N44" t="str">
+      <c r="S44" t="b">
+        <f>small!U28</f>
+        <v>1</v>
+      </c>
+      <c r="T44" t="str">
         <f>small!S5</f>
         <v>DNF</v>
       </c>
-      <c r="Q44" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R44" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S44" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W44" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X44" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U44" t="b">
+        <f>small!V28</f>
+        <v>1</v>
+      </c>
+      <c r="W44" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X44" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y44" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC44" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD44" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B45">
         <v>4.2738648947951301</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45">
         <v>0.21373200442967899</v>
       </c>
-      <c r="D45">
+      <c r="E45" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45">
         <v>0.88338870431893701</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45">
         <v>4.359990700918285</v>
       </c>
-      <c r="H45">
+      <c r="J45" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45">
         <v>0.21015924677438103</v>
       </c>
-      <c r="I45">
+      <c r="L45" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>0.99232825758456356</v>
       </c>
-      <c r="L45" t="str">
+      <c r="N45" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="str">
         <f>small!Q6</f>
         <v>DNF</v>
       </c>
-      <c r="M45" t="str">
+      <c r="Q45" t="b">
+        <f>small!T29</f>
+        <v>1</v>
+      </c>
+      <c r="R45" t="str">
         <f>small!R6</f>
         <v>DNF</v>
       </c>
-      <c r="N45" t="str">
+      <c r="S45" t="b">
+        <f>small!U29</f>
+        <v>1</v>
+      </c>
+      <c r="T45" t="str">
         <f>small!S6</f>
         <v>DNF</v>
       </c>
-      <c r="Q45" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R45" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S45" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W45" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X45" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U45" t="b">
+        <f>small!V29</f>
+        <v>1</v>
+      </c>
+      <c r="W45" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X45" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y45" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC45" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD45" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B46">
         <v>14.2153125609835</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46">
         <v>0.17338840824822699</v>
       </c>
-      <c r="D46">
+      <c r="E46" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46">
         <v>0.86173811227476704</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46">
         <v>11.888163212518995</v>
       </c>
-      <c r="H46">
+      <c r="J46" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46">
         <v>0.19266707620679618</v>
       </c>
-      <c r="I46">
+      <c r="L46" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46">
         <v>0.90620453296259174</v>
       </c>
-      <c r="L46" t="str">
+      <c r="N46" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="str">
         <f>small!Q7</f>
         <v>DNF</v>
       </c>
-      <c r="M46" t="str">
+      <c r="Q46" t="b">
+        <f>small!T30</f>
+        <v>1</v>
+      </c>
+      <c r="R46" t="str">
         <f>small!R7</f>
         <v>DNF</v>
       </c>
-      <c r="N46" t="str">
+      <c r="S46" t="b">
+        <f>small!U30</f>
+        <v>1</v>
+      </c>
+      <c r="T46" t="str">
         <f>small!S7</f>
         <v>DNF</v>
       </c>
-      <c r="Q46" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R46" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S46" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W46" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X46" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U46" t="b">
+        <f>small!V30</f>
+        <v>1</v>
+      </c>
+      <c r="W46" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X46" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y46" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
+      <c r="AB46" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC46" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD46" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B47">
         <v>6.5668754605748001</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47">
         <v>0.21536477523949901</v>
       </c>
-      <c r="D47">
+      <c r="E47" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47">
         <v>0.83124539425202704</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <v>6.8156616754350461</v>
       </c>
-      <c r="H47">
+      <c r="J47" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47">
         <v>0.24170376365843788</v>
       </c>
-      <c r="I47">
+      <c r="L47" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>1.0780048563334681</v>
       </c>
-      <c r="L47" t="str">
+      <c r="N47" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="str">
         <f>small!Q8</f>
         <v>DNF</v>
       </c>
-      <c r="M47" t="str">
+      <c r="Q47" t="b">
+        <f>small!T31</f>
+        <v>1</v>
+      </c>
+      <c r="R47" t="str">
         <f>small!R8</f>
         <v>DNF</v>
       </c>
-      <c r="N47" t="str">
+      <c r="S47" t="b">
+        <f>small!U31</f>
+        <v>1</v>
+      </c>
+      <c r="T47" t="str">
         <f>small!S8</f>
         <v>DNF</v>
       </c>
-      <c r="Q47" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R47" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S47" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W47" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X47" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U47" t="b">
+        <f>small!V31</f>
+        <v>1</v>
+      </c>
+      <c r="W47" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X47" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y47" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC47" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD47" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B48">
         <v>7.3333064970614297</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48">
         <v>0.125915787778762</v>
       </c>
-      <c r="D48">
+      <c r="E48" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48">
         <v>0.85085741888736799</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48">
         <v>5.9027614236335326</v>
       </c>
-      <c r="H48">
+      <c r="J48" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48">
         <v>9.321229156379382E-2</v>
       </c>
-      <c r="I48">
+      <c r="L48" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48">
         <v>0.79583697344931059</v>
       </c>
-      <c r="L48" t="str">
+      <c r="N48" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="str">
         <f>small!Q9</f>
         <v>DNF</v>
       </c>
-      <c r="M48" t="str">
+      <c r="Q48" t="b">
+        <f>small!T32</f>
+        <v>1</v>
+      </c>
+      <c r="R48" t="str">
         <f>small!R9</f>
         <v>DNF</v>
       </c>
-      <c r="N48" t="str">
+      <c r="S48" t="b">
+        <f>small!U32</f>
+        <v>1</v>
+      </c>
+      <c r="T48" t="str">
         <f>small!S9</f>
         <v>DNF</v>
       </c>
-      <c r="Q48" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R48" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S48" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W48" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X48" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U48" t="b">
+        <f>small!V32</f>
+        <v>1</v>
+      </c>
+      <c r="W48" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X48" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y48" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC48" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD48" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B49">
         <v>6.0736645962732903</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D49">
         <v>0.23950310559006199</v>
       </c>
-      <c r="D49">
+      <c r="E49" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49">
         <v>0.79888198757763995</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49">
         <v>6.3449671925171023</v>
       </c>
-      <c r="H49">
+      <c r="J49" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49">
         <v>0.2921960072595281</v>
       </c>
-      <c r="I49">
+      <c r="L49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>0.65014658662571545</v>
       </c>
-      <c r="L49" t="str">
+      <c r="N49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="str">
         <f>small!Q10</f>
         <v>DNF</v>
       </c>
-      <c r="M49" t="str">
+      <c r="Q49" t="b">
+        <f>small!T33</f>
+        <v>1</v>
+      </c>
+      <c r="R49" t="str">
         <f>small!R10</f>
         <v>DNF</v>
       </c>
-      <c r="N49" t="str">
+      <c r="S49" t="b">
+        <f>small!U33</f>
+        <v>1</v>
+      </c>
+      <c r="T49" t="str">
         <f>small!S10</f>
         <v>DNF</v>
       </c>
-      <c r="Q49" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R49" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S49" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W49" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X49" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U49" t="b">
+        <f>small!V33</f>
+        <v>1</v>
+      </c>
+      <c r="W49" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X49" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y49" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC49" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD49" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B50">
         <v>30.3209635416667</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D50">
         <v>0.299560546875</v>
       </c>
-      <c r="D50">
+      <c r="E50" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50">
         <v>0.7666015625</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50">
         <v>26.313826940231937</v>
       </c>
-      <c r="H50">
+      <c r="J50" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50">
         <v>0.22132024977698486</v>
       </c>
-      <c r="I50">
+      <c r="L50" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50">
         <v>0.85093666369313126</v>
       </c>
-      <c r="L50" t="str">
+      <c r="N50" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="str">
         <f>small!Q11</f>
         <v>DNF</v>
       </c>
-      <c r="M50" t="str">
+      <c r="Q50" t="b">
+        <f>small!T34</f>
+        <v>1</v>
+      </c>
+      <c r="R50" t="str">
         <f>small!R11</f>
         <v>DNF</v>
       </c>
-      <c r="N50" t="str">
+      <c r="S50" t="b">
+        <f>small!U34</f>
+        <v>1</v>
+      </c>
+      <c r="T50" t="str">
         <f>small!S11</f>
         <v>DNF</v>
       </c>
-      <c r="Q50" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R50" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S50" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W50" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X50" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U50" t="b">
+        <f>small!V34</f>
+        <v>1</v>
+      </c>
+      <c r="W50" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X50" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y50" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
+      <c r="AB50" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC50" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD50" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B51">
         <v>5.6813829038163597</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51">
         <v>0.153640332347557</v>
       </c>
-      <c r="D51">
+      <c r="E51" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51">
         <v>0.912899591606816</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51">
         <v>4.0623899085175292</v>
       </c>
-      <c r="H51">
+      <c r="J51" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51">
         <v>0.12074549690323315</v>
       </c>
-      <c r="I51">
+      <c r="L51" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51">
         <v>0.72595033808739129</v>
       </c>
-      <c r="L51" t="str">
+      <c r="N51" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="str">
         <f>small!Q12</f>
         <v>DNF</v>
       </c>
-      <c r="M51" t="str">
+      <c r="Q51" t="b">
+        <f>small!T35</f>
+        <v>1</v>
+      </c>
+      <c r="R51" t="str">
         <f>small!R12</f>
         <v>DNF</v>
       </c>
-      <c r="N51" t="str">
+      <c r="S51" t="b">
+        <f>small!U35</f>
+        <v>1</v>
+      </c>
+      <c r="T51" t="str">
         <f>small!S12</f>
         <v>DNF</v>
       </c>
-      <c r="Q51" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R51" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S51" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W51" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X51" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U51" t="b">
+        <f>small!V35</f>
+        <v>1</v>
+      </c>
+      <c r="W51" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X51" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y51" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC51" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD51" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B52">
         <v>4.5109378636257897</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52">
         <v>0.20805212939260001</v>
       </c>
-      <c r="D52">
+      <c r="E52" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>0.73074237840353695</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52">
         <v>5.4386168821734708</v>
       </c>
-      <c r="H52">
+      <c r="J52" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52">
         <v>0.31672235943629229</v>
       </c>
-      <c r="I52">
+      <c r="L52" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>0.85297108818829004</v>
       </c>
-      <c r="L52" t="str">
+      <c r="N52" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="str">
         <f>small!Q13</f>
         <v>DNF</v>
       </c>
-      <c r="M52" t="str">
+      <c r="Q52" t="b">
+        <f>small!T36</f>
+        <v>1</v>
+      </c>
+      <c r="R52" t="str">
         <f>small!R13</f>
         <v>DNF</v>
       </c>
-      <c r="N52" t="str">
+      <c r="S52" t="b">
+        <f>small!U36</f>
+        <v>1</v>
+      </c>
+      <c r="T52" t="str">
         <f>small!S13</f>
         <v>DNF</v>
       </c>
-      <c r="Q52" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R52" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S52" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W52" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X52" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U52" t="b">
+        <f>small!V36</f>
+        <v>1</v>
+      </c>
+      <c r="W52" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X52" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y52" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC52" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD52" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B53">
         <v>10.907756813417199</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D53">
         <v>0.40146750524108998</v>
       </c>
-      <c r="D53">
+      <c r="E53" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53">
         <v>1.0382599580712799</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53">
         <v>8.3449206884913938</v>
       </c>
-      <c r="H53">
+      <c r="J53" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53">
         <v>0.39082011474856571</v>
       </c>
-      <c r="I53">
+      <c r="L53" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53">
         <v>0.67285408932388358</v>
       </c>
-      <c r="L53" t="str">
+      <c r="N53" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="str">
         <f>small!Q14</f>
         <v>DNF</v>
       </c>
-      <c r="M53" t="str">
+      <c r="Q53" t="b">
+        <f>small!T37</f>
+        <v>1</v>
+      </c>
+      <c r="R53" t="str">
         <f>small!R14</f>
         <v>DNF</v>
       </c>
-      <c r="N53" t="str">
+      <c r="S53" t="b">
+        <f>small!U37</f>
+        <v>1</v>
+      </c>
+      <c r="T53" t="str">
         <f>small!S14</f>
         <v>DNF</v>
       </c>
-      <c r="Q53" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R53" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S53" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W53" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X53" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U53" t="b">
+        <f>small!V37</f>
+        <v>1</v>
+      </c>
+      <c r="W53" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X53" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y53" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC53" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD53" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B54">
         <v>6.1319916923297297</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D54">
         <v>0.18083506409797301</v>
       </c>
-      <c r="D54">
+      <c r="E54" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54">
         <v>1.0015039747905199</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54">
         <v>5.587720546385885</v>
       </c>
-      <c r="H54">
+      <c r="J54" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54">
         <v>0.14961582242458735</v>
       </c>
-      <c r="I54">
+      <c r="L54" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54">
         <v>1.0206317586795672</v>
       </c>
-      <c r="L54" t="str">
+      <c r="N54" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="str">
         <f>small!Q15</f>
         <v>DNF</v>
       </c>
-      <c r="M54" t="str">
+      <c r="Q54" t="b">
+        <f>small!T38</f>
+        <v>1</v>
+      </c>
+      <c r="R54" t="str">
         <f>small!R15</f>
         <v>DNF</v>
       </c>
-      <c r="N54" t="str">
+      <c r="S54" t="b">
+        <f>small!U38</f>
+        <v>1</v>
+      </c>
+      <c r="T54" t="str">
         <f>small!S15</f>
         <v>DNF</v>
       </c>
-      <c r="Q54" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R54" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S54" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W54" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X54" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U54" t="b">
+        <f>small!V38</f>
+        <v>1</v>
+      </c>
+      <c r="W54" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X54" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y54" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+      <c r="AB54" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC54" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD54" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B55">
         <v>5.5389721787126103</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D55">
         <v>0.17378981129260801</v>
       </c>
-      <c r="D55">
+      <c r="E55" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55">
         <v>0.83754754978742396</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55">
         <v>5.3358644859813085</v>
       </c>
-      <c r="H55">
+      <c r="J55" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55">
         <v>0.1908377837116155</v>
       </c>
-      <c r="I55">
+      <c r="L55" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55">
         <v>0.70635847797062756</v>
       </c>
-      <c r="L55" t="str">
+      <c r="N55" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="str">
         <f>small!Q16</f>
         <v>DNF</v>
       </c>
-      <c r="M55" t="str">
+      <c r="Q55" t="b">
+        <f>small!T39</f>
+        <v>1</v>
+      </c>
+      <c r="R55" t="str">
         <f>small!R16</f>
         <v>DNF</v>
       </c>
-      <c r="N55" t="str">
+      <c r="S55" t="b">
+        <f>small!U39</f>
+        <v>1</v>
+      </c>
+      <c r="T55" t="str">
         <f>small!S16</f>
         <v>DNF</v>
       </c>
-      <c r="Q55" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R55" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S55" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W55" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X55" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U55" t="b">
+        <f>small!V39</f>
+        <v>1</v>
+      </c>
+      <c r="W55" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X55" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y55" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
+      <c r="AB55" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC55" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD55" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B56">
         <v>4.4400217361771501</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56">
         <v>0.15514196440701</v>
       </c>
-      <c r="D56">
+      <c r="E56" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56">
         <v>0.80627632115201697</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56">
         <v>3.3562744004461793</v>
       </c>
-      <c r="H56">
+      <c r="J56" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56">
         <v>0.10362520914668154</v>
       </c>
-      <c r="I56">
+      <c r="L56" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56">
         <v>0.47105409927495817</v>
       </c>
-      <c r="L56" t="str">
+      <c r="N56" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="str">
         <f>small!Q17</f>
         <v>DNF</v>
       </c>
-      <c r="M56" t="str">
+      <c r="Q56" t="b">
+        <f>small!T40</f>
+        <v>1</v>
+      </c>
+      <c r="R56" t="str">
         <f>small!R17</f>
         <v>DNF</v>
       </c>
-      <c r="N56" t="str">
+      <c r="S56" t="b">
+        <f>small!U40</f>
+        <v>1</v>
+      </c>
+      <c r="T56" t="str">
         <f>small!S17</f>
         <v>DNF</v>
       </c>
-      <c r="Q56" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R56" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S56" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W56" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X56" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U56" t="b">
+        <f>small!V40</f>
+        <v>1</v>
+      </c>
+      <c r="W56" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X56" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y56" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+      <c r="AB56" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC56" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD56" s="8" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B57">
         <v>14.877283525845799</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57">
         <v>0.24379454411403301</v>
       </c>
-      <c r="D57">
+      <c r="E57" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57">
         <v>0.88858851478659795</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57">
         <v>11.815309842041311</v>
       </c>
-      <c r="H57">
+      <c r="J57" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57">
         <v>0.17950587282300526</v>
       </c>
-      <c r="I57">
+      <c r="L57" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57">
         <v>0.62179019846091532</v>
       </c>
-      <c r="L57" t="str">
+      <c r="N57" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="str">
         <f>small!Q18</f>
         <v>DNF</v>
       </c>
-      <c r="M57" t="str">
+      <c r="Q57" t="b">
+        <f>small!T41</f>
+        <v>1</v>
+      </c>
+      <c r="R57" t="str">
         <f>small!R18</f>
         <v>DNF</v>
       </c>
-      <c r="N57" t="str">
+      <c r="S57" t="b">
+        <f>small!U41</f>
+        <v>1</v>
+      </c>
+      <c r="T57" t="str">
         <f>small!S18</f>
         <v>DNF</v>
       </c>
-      <c r="Q57" s="4" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R57" s="4" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S57" s="4" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W57" s="8" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X57" s="8" t="e">
-        <f t="shared" si="23"/>
+      <c r="U57" t="b">
+        <f>small!V41</f>
+        <v>1</v>
+      </c>
+      <c r="W57" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X57" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y57" s="4" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+      <c r="AB57" s="8" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC57" s="8" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD57" s="8" t="e">
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Q2:X57">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>AND(Q2&lt;&gt;"",ISERROR(SEARCH("Both DNF",Q2)),ISNUMBER(Q2),Q2&gt;1.5)</formula>
+  <conditionalFormatting sqref="C3:C18">
+    <cfRule type="containsErrors" dxfId="54" priority="43">
+      <formula>ISERROR(C3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>AND(Q2&lt;&gt;"",ISERROR(SEARCH("Both DNF",Q2)),ISNUMBER(Q2),Q2&lt;0.5)</formula>
+    <cfRule type="cellIs" dxfId="53" priority="42" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:C38">
+    <cfRule type="containsErrors" dxfId="52" priority="49">
+      <formula>ISERROR(C23)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="48" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C42:C57">
+    <cfRule type="cellIs" dxfId="50" priority="54" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="containsErrors" dxfId="49" priority="55">
+      <formula>ISERROR(C42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E18">
+    <cfRule type="containsErrors" dxfId="48" priority="41">
+      <formula>ISERROR(E3)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="40" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E38">
+    <cfRule type="containsErrors" dxfId="46" priority="47">
+      <formula>ISERROR(E23)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="46" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42:E57">
+    <cfRule type="cellIs" dxfId="44" priority="52" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="containsErrors" dxfId="43" priority="53">
+      <formula>ISERROR(E42)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G18">
+    <cfRule type="containsErrors" dxfId="42" priority="39">
+      <formula>ISERROR(G3)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="38" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23:G38">
+    <cfRule type="containsErrors" dxfId="40" priority="45">
+      <formula>ISERROR(G23)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="44" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G42:G57">
+    <cfRule type="containsErrors" dxfId="38" priority="51">
+      <formula>ISERROR(G42)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="50" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J18">
+    <cfRule type="cellIs" dxfId="36" priority="30" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="containsErrors" dxfId="35" priority="31">
+      <formula>ISERROR(J3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23:J38">
+    <cfRule type="cellIs" dxfId="34" priority="24" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="containsErrors" dxfId="33" priority="25">
+      <formula>ISERROR(J23)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J42:J57">
+    <cfRule type="containsErrors" dxfId="32" priority="37">
+      <formula>ISERROR(J42)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="36" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L18">
+    <cfRule type="containsErrors" dxfId="30" priority="29">
+      <formula>ISERROR(L3)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L23:L38">
+    <cfRule type="cellIs" dxfId="28" priority="22" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="containsErrors" dxfId="27" priority="23">
+      <formula>ISERROR(L23)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L42:L57">
+    <cfRule type="containsErrors" dxfId="26" priority="35">
+      <formula>ISERROR(L42)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="34" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N18">
+    <cfRule type="containsErrors" dxfId="24" priority="27">
+      <formula>ISERROR(N3)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="14" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N23:N38">
+    <cfRule type="containsErrors" dxfId="22" priority="21">
+      <formula>ISERROR(N23)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="19" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N42:N57">
+    <cfRule type="containsErrors" dxfId="20" priority="33">
+      <formula>ISERROR(N42)</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="32" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:Q18">
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q23:Q38">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q42:Q57">
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3:S18">
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S23:S38">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S42:S57">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3:U18">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U23:U38">
+    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U42:U57">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W19:Y22">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>AND(W19&lt;&gt;"",ISERROR(SEARCH("Both DNF",W19)),ISNUMBER(W19),W19&lt;0.5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>AND(W19&lt;&gt;"",ISERROR(SEARCH("Both DNF",W19)),ISNUMBER(W19),W19&gt;1.5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W39:Y41">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>AND(W39&lt;&gt;"",ISERROR(SEARCH("Both DNF",W39)),ISNUMBER(W39),W39&gt;1.5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>AND(W39&lt;&gt;"",ISERROR(SEARCH("Both DNF",W39)),ISNUMBER(W39),W39&lt;0.5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:AD57">
+    <cfRule type="expression" dxfId="5" priority="56">
+      <formula>AND(W2&lt;&gt;"",ISERROR(SEARCH("Both DNF",W2)),ISNUMBER(W2),W2&gt;1.5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="57">
+      <formula>AND(W2&lt;&gt;"",ISERROR(SEARCH("Both DNF",W2)),ISNUMBER(W2),W2&lt;0.5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB39:AD41">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>AND(AB39&lt;&gt;"",ISERROR(SEARCH("Both DNF",AB39)),ISNUMBER(AB39),AB39&gt;1.5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>AND(AB39&lt;&gt;"",ISERROR(SEARCH("Both DNF",AB39)),ISNUMBER(AB39),AB39&lt;0.5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB19:AD22">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(AB19&lt;&gt;"",ISERROR(SEARCH("Both DNF",AB19)),ISNUMBER(AB19),AB19&gt;1.5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(AB19&lt;&gt;"",ISERROR(SEARCH("Both DNF",AB19)),ISNUMBER(AB19),AB19&lt;0.5)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20990,7 +23283,7 @@
         <v>9</v>
       </c>
       <c r="D98" s="4" t="str">
-        <f t="shared" ref="D98:G117" si="7">IF(ISNA(E44), $C$1, TEXT(E44, "0.000"))</f>
+        <f t="shared" ref="D98:G105" si="7">IF(ISNA(E44), $C$1, TEXT(E44, "0.000"))</f>
         <v>TO</v>
       </c>
       <c r="E98" s="4" t="str">
@@ -28185,7 +30478,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="str">
-        <f t="shared" ref="D98:G117" si="8">IF(ISNA(E44), $C$1, TEXT(E44, "0.000"))</f>
+        <f t="shared" ref="D98:G105" si="8">IF(ISNA(E44), $C$1, TEXT(E44, "0.000"))</f>
         <v>TO</v>
       </c>
       <c r="E98" t="str">
